--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECEE840-45F4-41F4-A670-551DC11D2A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E68665-369A-4126-8BCC-E1DCEF38F044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61275" yWindow="4650" windowWidth="33795" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -218,6 +218,20 @@
   </si>
   <si>
     <t>获取途径配置表</t>
+  </si>
+  <si>
+    <t>TbFuncOpenConfig</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FuncOpenConfig</t>
+  </si>
+  <si>
+    <t>通用配置表/系统开放配置表.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统开放配置表</t>
   </si>
 </sst>
 </file>
@@ -601,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -845,6 +859,26 @@
         <v>48</v>
       </c>
     </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E68665-369A-4126-8BCC-E1DCEF38F044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAA2991-B97B-48E7-ABBF-9D386A97DCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -186,10 +186,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>通用配置表/道具配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>通用配置表/音效配置表.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -213,10 +209,6 @@
     <t>GetWayConfig</t>
   </si>
   <si>
-    <t>通用配置表/获取途径配置表@道具配置表.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>获取途径配置表</t>
   </si>
   <si>
@@ -232,13 +224,21 @@
   </si>
   <si>
     <t>系统开放配置表</t>
+  </si>
+  <si>
+    <t>道具/道具配置表.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具/获取途径配置表@道具配置表.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,15 +275,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -308,18 +299,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -335,13 +323,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="2" builtinId="8"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -748,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>32</v>
@@ -756,19 +740,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -782,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>35</v>
@@ -799,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>38</v>
@@ -816,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>41</v>
@@ -833,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>44</v>
@@ -861,22 +845,22 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -886,9 +870,6 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="E6" r:id="rId1" xr:uid="{74D7948A-487D-4230-BBC9-A48DFAF97456}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/GameConfig/Datas/Defines/__tables__.xlsx
+++ b/GameConfig/Datas/Defines/__tables__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C731C3F-B043-4066-BBC7-018FD1651F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -390,19 +396,42 @@
   </si>
   <si>
     <t>随机名配置表</t>
+  </si>
+  <si>
+    <t>TbGuideGroupConfig</t>
+  </si>
+  <si>
+    <t>GuideGroupConfig</t>
+  </si>
+  <si>
+    <t>新手引导组配置表</t>
+  </si>
+  <si>
+    <t>TbGuideStepConfig</t>
+  </si>
+  <si>
+    <t>GuideStepConfig</t>
+  </si>
+  <si>
+    <t>新手引导步骤配置表</t>
+  </si>
+  <si>
+    <t>group_by:GroupId</t>
+  </si>
+  <si>
+    <t>新手引导组配置表@通用/新手引导配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手引导步骤配置表@通用/新手引导配置表.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,144 +447,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -570,198 +469,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -769,259 +488,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1033,74 +513,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1358,20 +786,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="26.8333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="25.0833333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="50.0833333333333" style="4" customWidth="1"/>
-    <col min="5" max="5" width="50.9166666666667" style="4" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="25.08203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="50.08203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="50.9140625" style="4" customWidth="1"/>
     <col min="6" max="6" width="84.25" style="4" customWidth="1"/>
     <col min="7" max="7" width="31.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="55.25" style="4" customWidth="1"/>
@@ -1381,7 +809,7 @@
     <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1448,7 +876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1471,24 +899,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>31</v>
       </c>
@@ -1498,18 +926,18 @@
       <c r="D5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="4" t="b">
@@ -1518,13 +946,12 @@
       <c r="E6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="5"/>
       <c r="I6" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="5" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1540,7 +967,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>43</v>
       </c>
@@ -1550,14 +977,14 @@
       <c r="D8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
@@ -1567,31 +994,31 @@
       <c r="D9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>55</v>
       </c>
@@ -1601,14 +1028,14 @@
       <c r="D11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>57</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
@@ -1618,15 +1045,15 @@
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>61</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="5" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -1635,18 +1062,15 @@
       <c r="D13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
       <c r="I13" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="5" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1655,7 +1079,7 @@
       <c r="D14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -1665,8 +1089,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -1675,15 +1099,15 @@
       <c r="D15" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>74</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -1692,15 +1116,15 @@
       <c r="D16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>78</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="B17" s="5" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -1709,15 +1133,15 @@
       <c r="D17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="B18" s="5" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -1726,7 +1150,7 @@
       <c r="D18" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>86</v>
       </c>
       <c r="I18" s="4" t="s">
@@ -1736,8 +1160,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="B19" s="5" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -1746,7 +1170,7 @@
       <c r="D19" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>91</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -1759,153 +1183,187 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="D22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:10">
-      <c r="A21" s="6" t="s">
+    <row r="23" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:10">
-      <c r="A22" s="7" t="s">
+    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B24" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="B23" s="5" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="D25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H25" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I25" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="B24" s="5" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8" t="s">
+      <c r="D26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="4" t="s">
+      <c r="I26" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
-      <c r="B25" s="5" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="D27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="B26" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="B27" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>120</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>